--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:49:00+00:00</t>
+    <t>2026-09-08T10:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:17:39+00:00</t>
+    <t>2026-09-08T17:27:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T17:27:06+00:00</t>
+    <t>2026-09-09T08:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:16:24+00:00</t>
+    <t>2026-09-09T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:16:47+00:00</t>
+    <t>2026-09-09T12:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot.rc5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:21:13+00:00</t>
+    <t>2026-09-09T13:32:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:32:22+00:00</t>
+    <t>2026-09-09T14:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:23:03+00:00</t>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/master/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc5</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
